--- a/Configs/GameConfig/Datas/fg/#TerritoryControl-领地控制.xlsx
+++ b/Configs/GameConfig/Datas/fg/#TerritoryControl-领地控制.xlsx
@@ -581,7 +581,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>silent_mind</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">

--- a/Configs/GameConfig/Datas/fg/#TerritoryControl-领地控制.xlsx
+++ b/Configs/GameConfig/Datas/fg/#TerritoryControl-领地控制.xlsx
@@ -635,12 +635,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>foundry.strider,foundry.strider,foundry.armorbot</t>
+          <t>foundry.strider,foundry.armorbot,foundry.minelayer,foundry.strider,foundry.loader</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>foundry.armorbot,foundry.strider</t>
+          <t>foundry.siege_heavy,foundry.armorbot</t>
         </is>
       </c>
       <c r="G5" t="n">

--- a/Configs/GameConfig/Datas/fg/#TerritoryControl-领地控制.xlsx
+++ b/Configs/GameConfig/Datas/fg/#TerritoryControl-领地控制.xlsx
@@ -679,12 +679,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>clarity.sprayer,clarity.corrosion_swarm,clarity.oil_crawler,clarity.corrosion_swarm,clarity.ln2_pump</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>clarity.settling_tank,clarity.ln2_pump</t>
         </is>
       </c>
       <c r="G6" t="n">
